--- a/docs/web-experience/14-page-map.xlsx
+++ b/docs/web-experience/14-page-map.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>新P1（スライド26）</t>
+          <t>新P1（スライド25）</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>新P2（スライド27）</t>
+          <t>新P2（スライド26）</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -575,7 +575,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>新P3（スライド28）</t>
+          <t>新P3（スライド27）</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>新P4（スライド29）</t>
+          <t>新P4（スライド28）</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>新P5（スライド30）</t>
+          <t>新P5（スライド29）</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>新P6（スライド31）</t>
+          <t>新P6（スライド30）</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>新P7（スライド32）</t>
+          <t>新P7（スライド31）</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -751,7 +751,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>新P6（スライド31）（q-P1-Q1#1 に統合）</t>
+          <t>新P6（スライド30）（q-P1-Q1#1 に統合）</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>新P8（スライド33）</t>
+          <t>新P8（スライド32）</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>新P9（スライド34）</t>
+          <t>新P9（スライド33）</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>新P10（スライド35）</t>
+          <t>新P10（スライド34）</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>新P11（スライド36）</t>
+          <t>新P11（スライド35）</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>新P12（スライド37）</t>
+          <t>新P12（スライド36）</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>新P13（スライド38）</t>
+          <t>新P13（スライド37）</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>新P13（スライド38）（q-P1-Q2#1 に統合）</t>
+          <t>新P13（スライド37）（q-P1-Q2#1 に統合）</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>新P14（スライド39）</t>
+          <t>新P14（スライド38）</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>新P15（スライド40）</t>
+          <t>新P15（スライド39）</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>新P16（スライド41）</t>
+          <t>新P16（スライド40）</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>新P17（スライド42）</t>
+          <t>新P17（スライド41）</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>新P18（スライド43）</t>
+          <t>新P18（スライド42）</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>新P19（スライド44）</t>
+          <t>新P19（スライド43）</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>新P20（スライド45）</t>
+          <t>新P20（スライド44）</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>新P21（スライド46）</t>
+          <t>新P21（スライド45）</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>新P22（スライド47）</t>
+          <t>新P22（スライド46）</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>新P23（スライド48）</t>
+          <t>新P23（スライド47）</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>新P24（スライド49）</t>
+          <t>新P24（スライド48）</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>新P25（スライド50）</t>
+          <t>新P25（スライド49）</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>新P26（スライド51）</t>
+          <t>新P26（スライド50）</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>新P27（スライド52）</t>
+          <t>新P27（スライド51）</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>p2-q1-c#2（新P28（スライド53））、p2-q1-c#3（新P29（スライド54））</t>
+          <t>p2-q1-c#2（新P28（スライド52））、p2-q1-c#3（新P29（スライド53））</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>新P30（スライド55）</t>
+          <t>新P30（スライド54）</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>新P31（スライド56）</t>
+          <t>新P31（スライド55）</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>新P31（スライド56）（q-P2-Q2#1 に統合）</t>
+          <t>新P31（スライド55）（q-P2-Q2#1 に統合）</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>新P32（スライド57）</t>
+          <t>新P32（スライド56）</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>新P33（スライド58）</t>
+          <t>新P33（スライド57）</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>新P34（スライド59）</t>
+          <t>新P34（スライド58）</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>新P35（スライド60）</t>
+          <t>新P35（スライド59）</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>新P36（スライド61）</t>
+          <t>新P36（スライド60）</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>新P37（スライド62）</t>
+          <t>新P37（スライド61）</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>新P38（スライド63）</t>
+          <t>新P38（スライド62）</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>新P39（スライド64）</t>
+          <t>新P39（スライド63）</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>新P39（スライド64）（q-P3-Q1#1 に統合）</t>
+          <t>新P39（スライド63）（q-P3-Q1#1 に統合）</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>新P40（スライド65）</t>
+          <t>新P40（スライド64）</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>新P41（スライド66）</t>
+          <t>新P41（スライド65）</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>新P42（スライド67）</t>
+          <t>新P42（スライド66）</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>新P43（スライド68）</t>
+          <t>新P43（スライド67）</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>新P44（スライド69）</t>
+          <t>新P44（スライド68）</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>新P45（スライド70）</t>
+          <t>新P45（スライド69）</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>新P46（スライド71）</t>
+          <t>新P46（スライド70）</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>新P47（スライド72）</t>
+          <t>新P47（スライド71）</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>新P48（スライド73）</t>
+          <t>新P48（スライド72）</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>新P49（スライド74）</t>
+          <t>新P49（スライド73）</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>新P50（スライド75）</t>
+          <t>新P50（スライド74）</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>新P51（スライド76）</t>
+          <t>新P51（スライド75）</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>新P52（スライド77）</t>
+          <t>新P52（スライド76）</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>新P53（スライド78）</t>
+          <t>新P53（スライド77）</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>新P53（スライド78）（q-P4-Q1#1 に統合）</t>
+          <t>新P53（スライド77）（q-P4-Q1#1 に統合）</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>新P54（スライド79）</t>
+          <t>新P54（スライド78）</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>新P55（スライド80）</t>
+          <t>新P55（スライド79）</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>新P56（スライド81）</t>
+          <t>新P56（スライド80）</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>新P57（スライド82）</t>
+          <t>新P57（スライド81）</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>新P58（スライド83）</t>
+          <t>新P58（スライド82）</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>新P59（スライド84）</t>
+          <t>新P59（スライド83）</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>新P60（スライド85）</t>
+          <t>新P60（スライド84）</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>新P61（スライド86）</t>
+          <t>新P61（スライド85）</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>新P62（スライド87）</t>
+          <t>新P62（スライド86）</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>新P63（スライド88）</t>
+          <t>新P63（スライド87）</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>新P64（スライド89）</t>
+          <t>新P64（スライド88）</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>新P65（スライド90）</t>
+          <t>新P65（スライド89）</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>新P66（スライド91）</t>
+          <t>新P66（スライド90）</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>新P66（スライド91）（q-P4-Q3#1 に統合）</t>
+          <t>新P66（スライド90）（q-P4-Q3#1 に統合）</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>新P67（スライド92）</t>
+          <t>新P67（スライド91）</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>新P68（スライド93）</t>
+          <t>新P68（スライド92）</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>新P69（スライド94）</t>
+          <t>新P69（スライド93）</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>新P70（スライド95）</t>
+          <t>新P70（スライド94）</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>新P71（スライド96）</t>
+          <t>新P71（スライド95）</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>新P72（スライド97）</t>
+          <t>新P72（スライド96）</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>新P73（スライド98）</t>
+          <t>新P73（スライド97）</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>新P74（スライド99）</t>
+          <t>新P74（スライド98）</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>新P75（スライド100）</t>
+          <t>新P75（スライド99）</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>新P76（スライド101）</t>
+          <t>新P76（スライド100）</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>新P77（スライド102）</t>
+          <t>新P77（スライド101）</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>新P78（スライド103）</t>
+          <t>新P78（スライド102）</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>新P79（スライド104）</t>
+          <t>新P79（スライド103）</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
